--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9949</v>
+        <v>9694.950000000001</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10140.66</v>
+        <v>9881.709999999999</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1230.74</v>
+        <v>1199.31</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3475.4</v>
+        <v>3386.65</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>16288.04</v>
+        <v>15872.11</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1404.09</v>
+        <v>1376.71</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3348.01</v>
+        <v>3282.71</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3675.25</v>
+        <v>3603.56</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1692.56</v>
+        <v>1659.55</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1788.5</v>
+        <v>1753.62</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2052.25</v>
+        <v>2012.22</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>804.47</v>
+        <v>788.78</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4423.3</v>
+        <v>4337.02</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3220.12</v>
+        <v>3144.8</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5268.94</v>
+        <v>5145.68</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4633.57</v>
+        <v>4525.17</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2882.98</v>
+        <v>2815.54</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2014.73</v>
+        <v>1967.6</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3618.6</v>
+        <v>3533.95</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>826.52</v>
+        <v>807.1900000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4128.01</v>
+        <v>4031.44</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2320.21</v>
+        <v>2265.94</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9668.450000000001</v>
+        <v>9442.27</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1992.38</v>
+        <v>1945.78</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3212.02</v>
+        <v>3165.98</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>998.98</v>
+        <v>984.66</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1286.1</v>
+        <v>1267.66</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1257.32</v>
+        <v>1239.29</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3504.44</v>
+        <v>3454.21</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1071.92</v>
+        <v>1056.55</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1034.72</v>
+        <v>1019.89</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>974.04</v>
+        <v>960.08</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1026.23</v>
+        <v>1011.52</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1766.18</v>
+        <v>1740.87</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3092.25</v>
+        <v>3047.93</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2139.93</v>
+        <v>2109.26</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3578.49</v>
+        <v>3527.19</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2549.97</v>
+        <v>2513.42</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>9660.610000000001</v>
+        <v>9522.139999999999</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1208.4</v>
+        <v>1191.08</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>830.23</v>
+        <v>818.33</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>828.3200000000001</v>
+        <v>816.45</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1508.07</v>
+        <v>1486.45</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1352.37</v>
+        <v>1332.99</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>798.6</v>
+        <v>787.15</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1837.98</v>
+        <v>1811.63</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1277.51</v>
+        <v>1259.2</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3708.5</v>
+        <v>3661.43</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>791.63</v>
+        <v>781.59</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1405.49</v>
+        <v>1387.65</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>6576.33</v>
+        <v>6492.86</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2636.41</v>
+        <v>2602.95</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2008.22</v>
+        <v>1982.73</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3298.14</v>
+        <v>3256.28</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2212.23</v>
+        <v>2184.15</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>791.78</v>
+        <v>781.73</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2677.83</v>
+        <v>2643.84</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4125.21</v>
+        <v>4072.85</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1115.94</v>
+        <v>1101.77</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2033.42</v>
+        <v>2007.61</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>6592.64</v>
+        <v>6508.96</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1388.1</v>
+        <v>1370.48</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3580.09</v>
+        <v>3534.64</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6397.31</v>
+        <v>6316.11</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>9046.43</v>
+        <v>8931.610000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>891.73</v>
+        <v>880.41</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2302.01</v>
+        <v>2272.79</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2663.67</v>
+        <v>2625.29</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5639.59</v>
+        <v>5558.33</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2832.55</v>
+        <v>2791.73</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1135.5</v>
+        <v>1119.14</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1311.34</v>
+        <v>1292.44</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1789.98</v>
+        <v>1764.19</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>76245.73</v>
+        <v>75147.02</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>811.61</v>
+        <v>799.92</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1263.68</v>
+        <v>1245.47</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>798.39</v>
+        <v>786.89</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>9947.389999999999</v>
+        <v>9804.040000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2288.55</v>
+        <v>2255.57</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>799.05</v>
+        <v>787.53</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5175.09</v>
+        <v>5100.51</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2636.41</v>
+        <v>2598.42</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>5842.74</v>
+        <v>5758.54</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4650.58</v>
+        <v>4583.56</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3638.78</v>
+        <v>3586.35</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5657.59</v>
+        <v>5576.06</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>7020.46</v>
+        <v>6919.3</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2789.34</v>
+        <v>2749.14</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>845.96</v>
+        <v>833.77</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>4630.53</v>
+        <v>4563.81</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2607.33</v>
+        <v>2569.76</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>857.72</v>
+        <v>845.36</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>6758.63</v>
+        <v>6661.23</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3014.42</v>
+        <v>2970.99</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2698.34</v>
+        <v>2659.45</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5768.75</v>
+        <v>5685.62</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>30367.77</v>
+        <v>29930.16</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2179.98</v>
+        <v>2148.57</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>7716.45</v>
+        <v>7605.26</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3107.3</v>
+        <v>3062.52</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5521.6</v>
+        <v>5442.03</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1759.4</v>
+        <v>1736.66</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2108.17</v>
+        <v>2080.93</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1730.72</v>
+        <v>1708.35</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>809.7</v>
+        <v>799.24</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2888.29</v>
+        <v>2850.96</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>973.48</v>
+        <v>960.9</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>7561.26</v>
+        <v>7463.54</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>794.71</v>
+        <v>784.4400000000001</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>813.23</v>
+        <v>802.72</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>995.1799999999999</v>
+        <v>982.3200000000001</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1670.79</v>
+        <v>1649.19</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>829.26</v>
+        <v>818.54</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>891.48</v>
+        <v>879.96</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>793.03</v>
+        <v>782.78</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4142.94</v>
+        <v>4089.39</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1446.19</v>
+        <v>1427.5</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>912.8</v>
+        <v>901</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2316.42</v>
+        <v>2286.48</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2322.08</v>
+        <v>2292.07</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1220.08</v>
+        <v>1204.31</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2067.77</v>
+        <v>2041.05</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>5466.51</v>
+        <v>5395.86</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1091.98</v>
+        <v>1077.86</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3324.31</v>
+        <v>3317.76</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3774.98</v>
+        <v>3767.54</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>4285.83</v>
+        <v>4277.39</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2966.5</v>
+        <v>2960.66</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3804.11</v>
+        <v>3796.61</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1868.11</v>
+        <v>1864.43</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1238.64</v>
+        <v>1236.2</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1486.21</v>
+        <v>1483.28</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1105.54</v>
+        <v>1103.37</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>891.73</v>
+        <v>889.97</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>5654.78</v>
+        <v>5643.65</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>790.59</v>
+        <v>789.03</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>11146.59</v>
+        <v>11124.63</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>885.59</v>
+        <v>883.84</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2633.11</v>
+        <v>2627.93</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3483.8</v>
+        <v>3476.94</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>8903.809999999999</v>
+        <v>8886.27</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>917.5700000000001</v>
+        <v>915.77</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1437.46</v>
+        <v>1434.63</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>3832.81</v>
+        <v>3825.26</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>14704.13</v>
+        <v>14675.17</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1467.12</v>
+        <v>1464.23</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>12951.98</v>
+        <v>12926.48</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2231.86</v>
+        <v>2227.47</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>867.23</v>
+        <v>865.52</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>850.21</v>
+        <v>848.54</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>17626.34</v>
+        <v>17591.62</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>968.91</v>
+        <v>967</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>3827.14</v>
+        <v>3819.6</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1363.84</v>
+        <v>1363.85</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1267.15</v>
+        <v>1267.16</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2092.07</v>
+        <v>2092.09</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1711.56</v>
+        <v>1711.57</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1747.51</v>
+        <v>1747.52</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2505.83</v>
+        <v>2505.85</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2578.86</v>
+        <v>2578.88</v>
       </c>
     </row>
     <row r="162">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2015.09</v>
+        <v>2015.11</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2180.72</v>
+        <v>2180.73</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2139.66</v>
+        <v>2139.67</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>6420.73</v>
+        <v>6420.77</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3960.27</v>
+        <v>3960.29</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1983.1</v>
+        <v>1983.11</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1635.41</v>
+        <v>1635.42</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1165.36</v>
+        <v>1165.37</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>4521.32</v>
+        <v>4521.35</v>
       </c>
     </row>
     <row r="172">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>986.42</v>
+        <v>986.4299999999999</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>7932.61</v>
+        <v>7932.66</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2176.32</v>
+        <v>2176.33</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>941.8</v>
+        <v>941.8099999999999</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>5471.63</v>
+        <v>5479.23</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>6200.41</v>
+        <v>6209.02</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>15067.69</v>
+        <v>15088.61</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1030.15</v>
+        <v>1031.58</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>799.33</v>
+        <v>800.4400000000001</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2318.84</v>
+        <v>2322.06</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>791.76</v>
+        <v>792.86</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1838.72</v>
+        <v>1841.27</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1295.05</v>
+        <v>1296.85</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>4788.26</v>
+        <v>4794.91</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>790.62</v>
+        <v>791.72</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2477.02</v>
+        <v>2480.46</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>14027.43</v>
+        <v>14046.91</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1662.81</v>
+        <v>1665.12</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>7888.48</v>
+        <v>7899.43</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>8477.77</v>
+        <v>8489.540000000001</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>789.83</v>
+        <v>790.9299999999999</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1468.83</v>
+        <v>1470.87</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>807.39</v>
+        <v>808.51</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>995.75</v>
+        <v>997.13</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>14582.13</v>
+        <v>14602.38</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1461.91</v>
+        <v>1463.94</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2206.97</v>
+        <v>2210.04</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3134.85</v>
+        <v>3139.21</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2118.74</v>
+        <v>2121.68</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>10564.35</v>
+        <v>10579.02</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1745.89</v>
+        <v>1748.32</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>31561.8</v>
+        <v>31605.63</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1572.53</v>
+        <v>1574.71</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1189.04</v>
+        <v>1190.69</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1057.09</v>
+        <v>1058.56</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1718.84</v>
+        <v>1721.22</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1434.7</v>
+        <v>1436.69</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1038.87</v>
+        <v>1040.31</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>3244.26</v>
+        <v>3248.77</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>4222.68</v>
+        <v>4228.54</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1821.48</v>
+        <v>1824.01</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>812.6</v>
+        <v>813.73</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>7236.53</v>
+        <v>7246.58</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3039.15</v>
+        <v>3043.37</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2019.73</v>
+        <v>2018.35</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>3686.21</v>
+        <v>3683.69</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>993.23</v>
+        <v>992.55</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1304.35</v>
+        <v>1303.46</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>8101.2</v>
+        <v>8095.66</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>3839.49</v>
+        <v>3836.86</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>3905.75</v>
+        <v>3903.08</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1715.5</v>
+        <v>1714.33</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3978</v>
+        <v>3975.29</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>794.52</v>
+        <v>793.97</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1233.8</v>
+        <v>1232.96</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2233.19</v>
+        <v>2231.67</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2270.24</v>
+        <v>2268.69</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>3253.23</v>
+        <v>3251.01</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>5390.42</v>
+        <v>5386.74</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>968.66</v>
+        <v>968</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1559.01</v>
+        <v>1557.94</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>6839.27</v>
+        <v>6834.59</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>13390.04</v>
+        <v>13380.89</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2394.93</v>
+        <v>2393.29</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>11633.91</v>
+        <v>11625.97</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>36888.47</v>
+        <v>36863.27</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>6858.38</v>
+        <v>6853.7</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>930.4</v>
+        <v>929.77</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>38407.01</v>
+        <v>38380.77</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1791.53</v>
+        <v>1790.31</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2791.12</v>
+        <v>2789.21</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>793.87</v>
+        <v>793.33</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1794.34</v>
+        <v>1788.18</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>902.08</v>
+        <v>898.98</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1783.57</v>
+        <v>1777.45</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1269.88</v>
+        <v>1265.52</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1081.95</v>
+        <v>1078.23</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2635.87</v>
+        <v>2626.82</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>953.79</v>
+        <v>950.52</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2314.13</v>
+        <v>2306.19</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1829.86</v>
+        <v>1823.58</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2598.04</v>
+        <v>2589.13</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>6569.49</v>
+        <v>6546.94</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>16936.65</v>
+        <v>16878.52</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1313.75</v>
+        <v>1309.24</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1055.36</v>
+        <v>1051.74</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1815.11</v>
+        <v>1808.88</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1828.22</v>
+        <v>1821.94</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>21289.88</v>
+        <v>21216.81</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>853.4299999999999</v>
+        <v>850.5</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1043.52</v>
+        <v>1039.94</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>2730.32</v>
+        <v>2720.95</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>6343.86</v>
+        <v>6322.09</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>4604.38</v>
+        <v>4588.58</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>3456.69</v>
+        <v>3444.83</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>13940.5</v>
+        <v>13892.66</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2663.23</v>
+        <v>2654.09</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>7645.53</v>
+        <v>7619.29</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>4324.96</v>
+        <v>4310.11</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1175.3</v>
+        <v>1169.1</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1641.63</v>
+        <v>1632.96</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>13894.19</v>
+        <v>13820.8</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>4763.95</v>
+        <v>4738.79</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3050.84</v>
+        <v>3034.72</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2243.78</v>
+        <v>2231.93</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1919.08</v>
+        <v>1908.95</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2690.99</v>
+        <v>2676.77</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1736.5</v>
+        <v>1727.33</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3200.92</v>
+        <v>3184.01</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>968.0599999999999</v>
+        <v>962.9400000000001</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>4115.72</v>
+        <v>4093.98</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2306.05</v>
+        <v>2293.87</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>808.73</v>
+        <v>804.46</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1748.1</v>
+        <v>1738.87</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1540.43</v>
+        <v>1532.29</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>5931.55</v>
+        <v>5900.22</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2644.33</v>
+        <v>2630.36</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2137.72</v>
+        <v>2126.43</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1220.23</v>
+        <v>1213.78</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>3317.32</v>
+        <v>3299.79</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1640.22</v>
+        <v>1631.55</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>4973.56</v>
+        <v>4947.29</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2260.73</v>
+        <v>2248.79</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>14143.12</v>
+        <v>14068.41</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1791.8</v>
+        <v>1782.34</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>9750.18</v>
+        <v>9698.68</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>3523.28</v>
+        <v>3504.67</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>4003.62</v>
+        <v>3982.47</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1947.19</v>
+        <v>1936.91</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>10549.21</v>
+        <v>10493.49</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1796.44</v>
+        <v>1786.96</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>6983.34</v>
+        <v>6946.45</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3716.92</v>
+        <v>3697.28</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1556.34</v>
+        <v>1548.11</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1107.93</v>
+        <v>1102.08</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>20473.22</v>
+        <v>20365.08</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>13643.26</v>
+        <v>13571.19</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1133.03</v>
+        <v>1127.05</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2462.16</v>
+        <v>2449.15</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2332.3</v>
+        <v>2319.98</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1313.67</v>
+        <v>1306.73</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>9611.91</v>
+        <v>9561.139999999999</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1719.76</v>
+        <v>1710.67</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>4057.6</v>
+        <v>4036.17</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1490.94</v>
+        <v>1483.06</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>7808.42</v>
+        <v>7767.17</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>6475.92</v>
+        <v>6441.71</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>3207.75</v>
+        <v>3187.64</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>954.97</v>
+        <v>948.99</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>16789.42</v>
+        <v>16684.21</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>998.71</v>
+        <v>992.46</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2579.34</v>
+        <v>2563.17</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2276.31</v>
+        <v>2262.04</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>4096.91</v>
+        <v>4071.24</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>26186.4</v>
+        <v>26022.3</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1727.85</v>
+        <v>1717.02</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>3754.86</v>
+        <v>3731.33</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>4743.91</v>
+        <v>4714.18</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>5188.28</v>
+        <v>5155.77</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>3765.34</v>
+        <v>3741.74</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>3343.83</v>
+        <v>3322.87</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>17108.26</v>
+        <v>17001.05</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>21417.37</v>
+        <v>21283.16</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>12220.19</v>
+        <v>12143.61</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>794.01</v>
+        <v>789.04</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>9156.1</v>
+        <v>9098.719999999999</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>2757.16</v>
+        <v>2739.89</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>792.98</v>
+        <v>788.01</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3732.98</v>
+        <v>3709.59</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>795.62</v>
+        <v>790.64</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2749.81</v>
+        <v>2732.58</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>1270.39</v>
+        <v>1262.43</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2932.99</v>
+        <v>2914.61</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>3757.29</v>
+        <v>3733.75</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>819.75</v>
+        <v>814.62</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>2076.2</v>
+        <v>2063.19</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1443.04</v>
+        <v>1433.99</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>795.61</v>
+        <v>790.62</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>7057.38</v>
+        <v>7013.16</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>61387</v>
+        <v>61002.32</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2074.96</v>
+        <v>2061.96</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1128.45</v>
+        <v>1121.37</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>3541.6</v>
+        <v>3519.41</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3504.13</v>
+        <v>3482.17</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>4491.86</v>
+        <v>4463.71</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1764.01</v>
+        <v>1752.96</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>8929.940000000001</v>
+        <v>8873.98</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>3944.95</v>
+        <v>3920.23</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>792.6799999999999</v>
+        <v>787.71</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>2851.43</v>
+        <v>2833.56</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>810.75</v>
+        <v>816.0700000000001</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>9650.540000000001</v>
+        <v>9713.790000000001</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1414</v>
+        <v>1423.27</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>996</v>
+        <v>1002.53</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>4333.15</v>
+        <v>4361.55</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>1243.33</v>
+        <v>1251.48</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1306.33</v>
+        <v>1314.89</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1092</v>
+        <v>1099.16</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>14482.82</v>
+        <v>14577.74</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>3294.5</v>
+        <v>3316.09</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>5950.33</v>
+        <v>5989.33</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1102.54</v>
+        <v>1109.77</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>27324.13</v>
+        <v>27503.21</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>3877.95</v>
+        <v>3903.37</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>790.12</v>
+        <v>795.29</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1600.64</v>
+        <v>1611.13</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>4954.85</v>
+        <v>4987.32</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>14849.78</v>
+        <v>14947.1</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>1389.96</v>
+        <v>1399.07</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1589.92</v>
+        <v>1600.34</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>5892.34</v>
+        <v>5930.96</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>6879.11</v>
+        <v>6924.2</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>2188.87</v>
+        <v>2203.21</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1748.26</v>
+        <v>1759.72</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>5305.65</v>
+        <v>5340.43</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>962.11</v>
+        <v>968.41</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>10270.85</v>
+        <v>10338.17</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>3220.81</v>
+        <v>3241.92</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>22179.31</v>
+        <v>22324.67</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>14986.44</v>
+        <v>15084.66</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>2115.74</v>
+        <v>2129.6</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>5464.47</v>
+        <v>5500.28</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>11744.28</v>
+        <v>11821.25</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>43576.69</v>
+        <v>43862.29</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>2453.21</v>
+        <v>2469.29</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2224.2</v>
+        <v>2238.78</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1502.26</v>
+        <v>1512.1</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1989.69</v>
+        <v>2002.73</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>8487.83</v>
+        <v>8543.459999999999</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>863.28</v>
+        <v>868.9400000000001</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>1803.69</v>
+        <v>1815.52</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>2588.75</v>
+        <v>2605.72</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>2070.32</v>
+        <v>2083.89</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>2309.93</v>
+        <v>2341.04</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>10932.36</v>
+        <v>11079.58</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>869.74</v>
+        <v>881.45</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>13464.75</v>
+        <v>13646.08</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>991.12</v>
+        <v>1004.46</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>959.02</v>
+        <v>971.9299999999999</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>5252.52</v>
+        <v>5323.25</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2837.3</v>
+        <v>2875.51</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>1892.09</v>
+        <v>1917.57</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>2184.68</v>
+        <v>2214.1</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1186.93</v>
+        <v>1202.92</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>2805.91</v>
+        <v>2843.7</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>6371.19</v>
+        <v>6456.98</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1466.76</v>
+        <v>1486.51</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>5390.59</v>
+        <v>5463.18</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1816.06</v>
+        <v>1840.51</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>796.53</v>
+        <v>807.26</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>2737.55</v>
+        <v>2774.42</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>1228.71</v>
+        <v>1245.26</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>1139.16</v>
+        <v>1154.5</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>1767.19</v>
+        <v>1790.99</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>2516.36</v>
+        <v>2550.25</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>14121.33</v>
+        <v>14311.5</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1367.75</v>
+        <v>1386.16</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>2828.1</v>
+        <v>2866.18</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>915.15</v>
+        <v>927.47</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>3150.06</v>
+        <v>3192.48</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>1374.21</v>
+        <v>1392.72</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>18106.47</v>
+        <v>18350.3</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>792.75</v>
+        <v>803.42</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>8206</v>
+        <v>8316.51</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>2723.01</v>
+        <v>2759.68</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>12289.46</v>
+        <v>12454.96</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>3277</v>
+        <v>3321.13</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>69588.75999999999</v>
+        <v>70525.87</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>3876.96</v>
+        <v>3929.16</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>3488.72</v>
+        <v>3535.7</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>5890.3</v>
+        <v>5969.62</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1694.34</v>
+        <v>1717.15</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>2149.22</v>
+        <v>2178.16</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>1128.17</v>
+        <v>1143.37</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2944.73</v>
+        <v>2984.39</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>66503.98</v>
+        <v>67399.55</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>1197.63</v>
+        <v>1213.76</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>4345.78</v>
+        <v>4404.3</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>951.28</v>
+        <v>964.09</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>3959.82</v>
+        <v>4013.15</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>24519.8</v>
+        <v>24849.99</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>12729.23</v>
+        <v>12900.65</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2373.66</v>
+        <v>2405.63</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>2108.54</v>
+        <v>2140.64</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>991.53</v>
+        <v>1006.63</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>5872.69</v>
+        <v>5962.1</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>3168.77</v>
+        <v>3217.01</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>3562.8</v>
+        <v>3617.04</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>3999.41</v>
+        <v>4060.3</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>3920.76</v>
+        <v>3980.45</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>6777.88</v>
+        <v>6881.06</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>2718.54</v>
+        <v>2759.92</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>821.9299999999999</v>
+        <v>834.4400000000001</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>839.26</v>
+        <v>852.04</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>4957.4</v>
+        <v>5032.88</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>2137.64</v>
+        <v>2170.18</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>1270.22</v>
+        <v>1289.55</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>10152.21</v>
+        <v>10306.77</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>11476.45</v>
+        <v>11651.17</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>2480.8</v>
+        <v>2518.57</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>922.45</v>
+        <v>936.49</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>11110.24</v>
+        <v>11279.38</v>
       </c>
     </row>
     <row r="475">
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>1196.35</v>
+        <v>1214.56</v>
       </c>
     </row>
     <row r="476">
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>2762.08</v>
+        <v>2804.13</v>
       </c>
     </row>
     <row r="477">
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>1980.32</v>
+        <v>2010.47</v>
       </c>
     </row>
     <row r="478">
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>791.92</v>
+        <v>803.98</v>
       </c>
     </row>
     <row r="479">
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>2591.49</v>
+        <v>2630.94</v>
       </c>
     </row>
     <row r="480">
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>800.84</v>
+        <v>813.03</v>
       </c>
     </row>
     <row r="481">
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>3166.28</v>
+        <v>3214.48</v>
       </c>
     </row>
     <row r="482">
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>3393.15</v>
+        <v>3444.81</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>803.01</v>
+        <v>815.24</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>12854.92</v>
+        <v>13050.63</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>2604.99</v>
+        <v>2644.65</v>
       </c>
     </row>
     <row r="486">
@@ -30093,7 +30093,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>5521.6</v>
+        <v>5605.66</v>
       </c>
     </row>
     <row r="487">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>844.88</v>
+        <v>857.74</v>
       </c>
     </row>
     <row r="488">
@@ -30215,7 +30215,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>1872.33</v>
+        <v>1900.83</v>
       </c>
     </row>
     <row r="489">
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>923.84</v>
+        <v>937.91</v>
       </c>
     </row>
     <row r="490">
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1232.59</v>
+        <v>1251.35</v>
       </c>
     </row>
     <row r="491">
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>51254.71</v>
+        <v>52035.02</v>
       </c>
     </row>
     <row r="492">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>2260.82</v>
+        <v>2295.24</v>
       </c>
     </row>
     <row r="493">
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1354.82</v>
+        <v>1387.76</v>
       </c>
     </row>
     <row r="494">
@@ -30581,7 +30581,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>4942.89</v>
+        <v>5063.09</v>
       </c>
     </row>
     <row r="495">
@@ -30642,7 +30642,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>10419.47</v>
+        <v>10672.84</v>
       </c>
     </row>
     <row r="496">
@@ -30703,7 +30703,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>3207.43</v>
+        <v>3285.43</v>
       </c>
     </row>
     <row r="497">
@@ -30764,7 +30764,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>14494.33</v>
+        <v>14846.8</v>
       </c>
     </row>
     <row r="498">
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>2247.51</v>
+        <v>2302.17</v>
       </c>
     </row>
     <row r="499">
@@ -30886,7 +30886,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>895.98</v>
+        <v>917.77</v>
       </c>
     </row>
     <row r="500">
@@ -30947,7 +30947,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>2873.88</v>
+        <v>2943.77</v>
       </c>
     </row>
     <row r="501">
@@ -31008,7 +31008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>5060.61</v>
+        <v>5183.68</v>
       </c>
     </row>
     <row r="502">
@@ -31069,7 +31069,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>8385.120000000001</v>
+        <v>8589.030000000001</v>
       </c>
     </row>
     <row r="503">
@@ -31130,7 +31130,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>1254.11</v>
+        <v>1284.61</v>
       </c>
     </row>
     <row r="504">
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>2690.61</v>
+        <v>2756.04</v>
       </c>
     </row>
     <row r="505">
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>1921.91</v>
+        <v>1968.65</v>
       </c>
     </row>
     <row r="506">
@@ -31313,7 +31313,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>10126.43</v>
+        <v>10372.68</v>
       </c>
     </row>
     <row r="507">
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>990.8099999999999</v>
+        <v>1014.9</v>
       </c>
     </row>
     <row r="508">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>794.84</v>
+        <v>814.17</v>
       </c>
     </row>
     <row r="509">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1268.22</v>
+        <v>1299.06</v>
       </c>
     </row>
     <row r="510">
@@ -31557,7 +31557,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>1086.05</v>
+        <v>1112.46</v>
       </c>
     </row>
     <row r="511">
@@ -31618,7 +31618,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>3944.84</v>
+        <v>4040.77</v>
       </c>
     </row>
     <row r="512">
@@ -31679,7 +31679,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>3227.07</v>
+        <v>3305.55</v>
       </c>
     </row>
     <row r="513">
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>2540.93</v>
+        <v>2602.72</v>
       </c>
     </row>
     <row r="514">
@@ -31801,7 +31801,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>2365.66</v>
+        <v>2423.19</v>
       </c>
     </row>
     <row r="515">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>790.92</v>
+        <v>810.15</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>1193.73</v>
+        <v>1222.76</v>
       </c>
     </row>
     <row r="517">
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>4326.44</v>
+        <v>4431.65</v>
       </c>
     </row>
     <row r="518">
@@ -32045,7 +32045,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>3882.46</v>
+        <v>3976.87</v>
       </c>
     </row>
     <row r="519">
@@ -32106,7 +32106,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>1770.51</v>
+        <v>1813.56</v>
       </c>
     </row>
     <row r="520">
@@ -32167,7 +32167,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>1109.27</v>
+        <v>1136.24</v>
       </c>
     </row>
     <row r="521">
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>8662.790000000001</v>
+        <v>8873.450000000001</v>
       </c>
     </row>
     <row r="522">
@@ -32289,7 +32289,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>4958.08</v>
+        <v>5078.65</v>
       </c>
     </row>
     <row r="523">
@@ -32350,7 +32350,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>2417.36</v>
+        <v>2476.14</v>
       </c>
     </row>
     <row r="524">
@@ -32411,7 +32411,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>3049.16</v>
+        <v>3123.31</v>
       </c>
     </row>
     <row r="525">
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>2889.39</v>
+        <v>2959.65</v>
       </c>
     </row>
     <row r="526">
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>19192.86</v>
+        <v>19659.59</v>
       </c>
     </row>
     <row r="527">
@@ -32594,7 +32594,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>22151.82</v>
+        <v>22690.5</v>
       </c>
     </row>
     <row r="528">
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>56897.89</v>
+        <v>58281.52</v>
       </c>
     </row>
     <row r="529">
@@ -32716,7 +32716,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1026.81</v>
+        <v>1051.78</v>
       </c>
     </row>
     <row r="530">
@@ -32777,7 +32777,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>11362.28</v>
+        <v>11638.58</v>
       </c>
     </row>
     <row r="531">
@@ -32838,7 +32838,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>837.76</v>
+        <v>858.13</v>
       </c>
     </row>
     <row r="532">
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>934.72</v>
+        <v>957.45</v>
       </c>
     </row>
     <row r="533">
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>56569.26</v>
+        <v>57944.9</v>
       </c>
     </row>
     <row r="534">
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>24985.42</v>
+        <v>25593.01</v>
       </c>
     </row>
     <row r="535">
@@ -33082,7 +33082,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>1535.82</v>
+        <v>1573.17</v>
       </c>
     </row>
     <row r="536">
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>963.71</v>
+        <v>987.14</v>
       </c>
     </row>
     <row r="537">
@@ -33204,7 +33204,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>60565.52</v>
+        <v>62038.33</v>
       </c>
     </row>
     <row r="538">
@@ -33265,7 +33265,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>1322.36</v>
+        <v>1354.52</v>
       </c>
     </row>
     <row r="539">
@@ -33326,7 +33326,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>2828.11</v>
+        <v>2896.88</v>
       </c>
     </row>
     <row r="540">
@@ -33387,7 +33387,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>4900.2</v>
+        <v>5019.36</v>
       </c>
     </row>
     <row r="541">
@@ -33448,7 +33448,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>791.38</v>
+        <v>810.62</v>
       </c>
     </row>
     <row r="542">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>910.1</v>
+        <v>932.23</v>
       </c>
     </row>
     <row r="543">
@@ -33570,7 +33570,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>850.05</v>
+        <v>871.54</v>
       </c>
     </row>
     <row r="544">
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>2643.85</v>
+        <v>2710.69</v>
       </c>
     </row>
     <row r="545">
@@ -33692,7 +33692,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>3273.71</v>
+        <v>3356.47</v>
       </c>
     </row>
     <row r="546">
@@ -33753,7 +33753,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>797.36</v>
+        <v>817.52</v>
       </c>
     </row>
     <row r="547">
@@ -33814,7 +33814,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>1422.94</v>
+        <v>1458.91</v>
       </c>
     </row>
     <row r="548">
@@ -33875,7 +33875,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>2288.01</v>
+        <v>2345.85</v>
       </c>
     </row>
     <row r="549">
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>961.64</v>
+        <v>985.95</v>
       </c>
     </row>
     <row r="550">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>1436.27</v>
+        <v>1472.58</v>
       </c>
     </row>
     <row r="551">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>2275.09</v>
+        <v>2332.6</v>
       </c>
     </row>
     <row r="552">
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>7928.17</v>
+        <v>8128.6</v>
       </c>
     </row>
     <row r="553">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>1720.79</v>
+        <v>1764.29</v>
       </c>
     </row>
     <row r="554">
@@ -34241,7 +34241,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>1203.98</v>
+        <v>1234.42</v>
       </c>
     </row>
     <row r="555">
@@ -34302,7 +34302,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>1138.89</v>
+        <v>1167.68</v>
       </c>
     </row>
     <row r="556">
@@ -34363,7 +34363,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>1490.61</v>
+        <v>1528.29</v>
       </c>
     </row>
     <row r="557">
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>2259.27</v>
+        <v>2316.39</v>
       </c>
     </row>
     <row r="558">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>1695.55</v>
+        <v>1738.41</v>
       </c>
     </row>
     <row r="559">
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>2498.8</v>
+        <v>2561.97</v>
       </c>
     </row>
     <row r="560">
@@ -34607,7 +34607,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>4377.05</v>
+        <v>4487.71</v>
       </c>
     </row>
     <row r="561">
@@ -34668,7 +34668,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>8391.42</v>
+        <v>8603.559999999999</v>
       </c>
     </row>
     <row r="562">
@@ -34729,7 +34729,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>4617.92</v>
+        <v>4734.66</v>
       </c>
     </row>
     <row r="563">
@@ -34790,7 +34790,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>1113.68</v>
+        <v>1141.84</v>
       </c>
     </row>
     <row r="564">
@@ -34851,7 +34851,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>2972.92</v>
+        <v>3048.07</v>
       </c>
     </row>
     <row r="565">
@@ -34912,7 +34912,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>3421.38</v>
+        <v>3507.88</v>
       </c>
     </row>
     <row r="566">
@@ -34973,7 +34973,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>792</v>
+        <v>812.02</v>
       </c>
     </row>
     <row r="567">
@@ -35034,7 +35034,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>1728.07</v>
+        <v>1771.76</v>
       </c>
     </row>
     <row r="568">
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>1134.74</v>
+        <v>1163.43</v>
       </c>
     </row>
     <row r="569">
@@ -35156,7 +35156,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>4545.48</v>
+        <v>4660.39</v>
       </c>
     </row>
     <row r="570">
@@ -35217,7 +35217,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>2699.41</v>
+        <v>2767.65</v>
       </c>
     </row>
     <row r="571">
@@ -35278,7 +35278,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>10352.96</v>
+        <v>10614.68</v>
       </c>
     </row>
     <row r="572">
@@ -35339,7 +35339,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>6529.1</v>
+        <v>6694.16</v>
       </c>
     </row>
     <row r="573">
@@ -35400,7 +35400,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>1407.75</v>
+        <v>1443.34</v>
       </c>
     </row>
     <row r="574">
@@ -35461,7 +35461,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>5129.05</v>
+        <v>5258.71</v>
       </c>
     </row>
     <row r="575">
@@ -35522,7 +35522,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>52485.94</v>
+        <v>53812.79</v>
       </c>
     </row>
     <row r="576">
@@ -35583,7 +35583,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>2755.33</v>
+        <v>2824.99</v>
       </c>
     </row>
     <row r="577">
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>2342.07</v>
+        <v>2401.28</v>
       </c>
     </row>
     <row r="578">
@@ -35705,7 +35705,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>1591.39</v>
+        <v>1631.62</v>
       </c>
     </row>
     <row r="579">
@@ -35766,7 +35766,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>813.2</v>
+        <v>837.86</v>
       </c>
     </row>
     <row r="580">
@@ -35827,7 +35827,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2589.18</v>
+        <v>2667.7</v>
       </c>
     </row>
     <row r="581">
@@ -35888,7 +35888,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>4492.62</v>
+        <v>4628.85</v>
       </c>
     </row>
     <row r="582">
@@ -35949,7 +35949,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>3554.79</v>
+        <v>3662.58</v>
       </c>
     </row>
     <row r="583">
@@ -36010,7 +36010,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>3079.52</v>
+        <v>3172.91</v>
       </c>
     </row>
     <row r="584">
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>2192.3</v>
+        <v>2258.77</v>
       </c>
     </row>
     <row r="585">
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>2844.79</v>
+        <v>2931.05</v>
       </c>
     </row>
     <row r="586">
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>2300.13</v>
+        <v>2369.87</v>
       </c>
     </row>
     <row r="587">
@@ -36254,7 +36254,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>994.29</v>
+        <v>1024.44</v>
       </c>
     </row>
     <row r="588">
@@ -36315,7 +36315,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1132.51</v>
+        <v>1166.85</v>
       </c>
     </row>
     <row r="589">
@@ -36376,7 +36376,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>29989.75</v>
+        <v>30899.13</v>
       </c>
     </row>
     <row r="590">
@@ -36437,7 +36437,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>1272.46</v>
+        <v>1311.04</v>
       </c>
     </row>
     <row r="591">
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>1646.29</v>
+        <v>1696.21</v>
       </c>
     </row>
     <row r="592">
@@ -36559,7 +36559,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>15744.55</v>
+        <v>16221.97</v>
       </c>
     </row>
     <row r="593">
@@ -36620,7 +36620,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>4586.35</v>
+        <v>4725.42</v>
       </c>
     </row>
     <row r="594">
@@ -36681,7 +36681,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>1809.28</v>
+        <v>1864.15</v>
       </c>
     </row>
     <row r="595">
@@ -36742,7 +36742,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>11538.33</v>
+        <v>11888.21</v>
       </c>
     </row>
     <row r="596">
@@ -36803,7 +36803,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>73352.41</v>
+        <v>75576.67999999999</v>
       </c>
     </row>
     <row r="597">
@@ -36864,7 +36864,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>3166.29</v>
+        <v>3262.3</v>
       </c>
     </row>
     <row r="598">
@@ -36925,7 +36925,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>2041.93</v>
+        <v>2103.84</v>
       </c>
     </row>
     <row r="599">
@@ -36986,7 +36986,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>1131.26</v>
+        <v>1165.56</v>
       </c>
     </row>
     <row r="600">
@@ -37047,7 +37047,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>2594.14</v>
+        <v>2672.8</v>
       </c>
     </row>
     <row r="601">
@@ -37108,7 +37108,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>1570.65</v>
+        <v>1618.27</v>
       </c>
     </row>
     <row r="602">
@@ -37169,7 +37169,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>791.33</v>
+        <v>815.3200000000001</v>
       </c>
     </row>
     <row r="603">
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>979.98</v>
+        <v>1009.7</v>
       </c>
     </row>
     <row r="604">
@@ -37291,7 +37291,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>8003.67</v>
+        <v>8246.370000000001</v>
       </c>
     </row>
     <row r="605">
@@ -37352,7 +37352,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>8487.4</v>
+        <v>8744.76</v>
       </c>
     </row>
     <row r="606">
@@ -37413,7 +37413,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>2923.08</v>
+        <v>3011.72</v>
       </c>
     </row>
     <row r="607">
@@ -37474,7 +37474,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>859.78</v>
+        <v>885.85</v>
       </c>
     </row>
     <row r="608">
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>839.29</v>
+        <v>864.74</v>
       </c>
     </row>
     <row r="609">
@@ -37596,7 +37596,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>5935.33</v>
+        <v>6115.31</v>
       </c>
     </row>
     <row r="610">
@@ -37657,7 +37657,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>2189.31</v>
+        <v>2255.69</v>
       </c>
     </row>
     <row r="611">
@@ -37718,7 +37718,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>851.38</v>
+        <v>877.1900000000001</v>
       </c>
     </row>
     <row r="612">
@@ -37779,7 +37779,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>13857.99</v>
+        <v>14278.21</v>
       </c>
     </row>
     <row r="613">
@@ -37840,7 +37840,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>1073.94</v>
+        <v>1106.5</v>
       </c>
     </row>
     <row r="614">
@@ -37901,7 +37901,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>1294.01</v>
+        <v>1333.25</v>
       </c>
     </row>
     <row r="615">
@@ -37962,7 +37962,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>2006.12</v>
+        <v>2066.95</v>
       </c>
     </row>
     <row r="616">
@@ -38023,7 +38023,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>2487.88</v>
+        <v>2563.32</v>
       </c>
     </row>
     <row r="617">
@@ -38084,7 +38084,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>817.9</v>
+        <v>842.7</v>
       </c>
     </row>
     <row r="618">
@@ -38145,7 +38145,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>5524.7</v>
+        <v>5692.22</v>
       </c>
     </row>
     <row r="619">
@@ -38206,7 +38206,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>9557.610000000001</v>
+        <v>9847.43</v>
       </c>
     </row>
     <row r="620">
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>5750.99</v>
+        <v>5925.38</v>
       </c>
     </row>
     <row r="621">
@@ -38328,7 +38328,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>812.71</v>
+        <v>837.35</v>
       </c>
     </row>
     <row r="622">
@@ -38389,7 +38389,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>2119.06</v>
+        <v>2183.32</v>
       </c>
     </row>
     <row r="623">
@@ -38450,7 +38450,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>17888.52</v>
+        <v>18430.95</v>
       </c>
     </row>
     <row r="624">
@@ -38511,7 +38511,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1862.07</v>
+        <v>1918.54</v>
       </c>
     </row>
     <row r="625">
@@ -38572,7 +38572,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>795.11</v>
+        <v>819.22</v>
       </c>
     </row>
     <row r="626">
@@ -38633,7 +38633,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>7127.45</v>
+        <v>7339.3</v>
       </c>
     </row>
     <row r="627">
@@ -38694,7 +38694,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>1556.16</v>
+        <v>1602.41</v>
       </c>
     </row>
     <row r="628">
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>2045.26</v>
+        <v>2106.06</v>
       </c>
     </row>
     <row r="629">
@@ -38816,7 +38816,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>790.89</v>
+        <v>814.4</v>
       </c>
     </row>
     <row r="630">
@@ -38877,7 +38877,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>2041.48</v>
+        <v>2102.16</v>
       </c>
     </row>
     <row r="631">
@@ -38938,7 +38938,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>4996.31</v>
+        <v>5144.81</v>
       </c>
     </row>
     <row r="632">
@@ -38999,7 +38999,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>34175.43</v>
+        <v>35191.23</v>
       </c>
     </row>
     <row r="633">
@@ -39060,7 +39060,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>1021.12</v>
+        <v>1051.48</v>
       </c>
     </row>
     <row r="634">
@@ -39121,7 +39121,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>3792.26</v>
+        <v>3904.98</v>
       </c>
     </row>
     <row r="635">
@@ -39182,7 +39182,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>4081.44</v>
+        <v>4202.75</v>
       </c>
     </row>
     <row r="636">
@@ -39243,7 +39243,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>4483.74</v>
+        <v>4617.01</v>
       </c>
     </row>
     <row r="637">
@@ -39304,7 +39304,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>1081.95</v>
+        <v>1114.1</v>
       </c>
     </row>
     <row r="638">
@@ -39365,7 +39365,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>974.64</v>
+        <v>1003.61</v>
       </c>
     </row>
     <row r="639">
@@ -39426,7 +39426,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>1658.66</v>
+        <v>1707.96</v>
       </c>
     </row>
     <row r="640">
@@ -39487,7 +39487,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>880.55</v>
+        <v>906.73</v>
       </c>
     </row>
     <row r="641">
@@ -39548,7 +39548,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>938.53</v>
+        <v>966.42</v>
       </c>
     </row>
     <row r="642">
@@ -39609,7 +39609,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>10223.01</v>
+        <v>10526.87</v>
       </c>
     </row>
     <row r="643">
@@ -39670,7 +39670,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>2327.59</v>
+        <v>2396.77</v>
       </c>
     </row>
     <row r="644">
@@ -39731,7 +39731,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>1143.68</v>
+        <v>1177.67</v>
       </c>
     </row>
     <row r="645">
@@ -39792,7 +39792,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>1304.07</v>
+        <v>1342.83</v>
       </c>
     </row>
     <row r="646">
@@ -39853,7 +39853,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>1499.84</v>
+        <v>1544.41</v>
       </c>
     </row>
     <row r="647">
@@ -39914,7 +39914,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>822.61</v>
+        <v>847.0599999999999</v>
       </c>
     </row>
     <row r="648">
@@ -39975,7 +39975,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>4459.25</v>
+        <v>4591.8</v>
       </c>
     </row>
     <row r="649">
@@ -40036,7 +40036,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>984.59</v>
+        <v>1013.86</v>
       </c>
     </row>
     <row r="650">
@@ -40097,7 +40097,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>793.53</v>
+        <v>817.11</v>
       </c>
     </row>
     <row r="651">
@@ -40158,7 +40158,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>11669.28</v>
+        <v>12016.12</v>
       </c>
     </row>
     <row r="652">
@@ -40219,7 +40219,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>796.6799999999999</v>
+        <v>820.36</v>
       </c>
     </row>
     <row r="653">
@@ -40280,7 +40280,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>45043.47</v>
+        <v>46382.29</v>
       </c>
     </row>
     <row r="654">
@@ -40341,7 +40341,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>2141.22</v>
+        <v>2204.87</v>
       </c>
     </row>
     <row r="655">
@@ -40402,7 +40402,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>1212.73</v>
+        <v>1248.78</v>
       </c>
     </row>
     <row r="656">
@@ -40463,7 +40463,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>6773.57</v>
+        <v>6974.9</v>
       </c>
     </row>
     <row r="657">
@@ -40524,7 +40524,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>1254.31</v>
+        <v>1291.59</v>
       </c>
     </row>
     <row r="658">
@@ -40585,7 +40585,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>9929.48</v>
+        <v>10224.62</v>
       </c>
     </row>
     <row r="659">
@@ -40646,7 +40646,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>3880.44</v>
+        <v>3995.78</v>
       </c>
     </row>
     <row r="660">
@@ -40707,7 +40707,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>1767.57</v>
+        <v>1820.11</v>
       </c>
     </row>
     <row r="661">
@@ -40768,7 +40768,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>3236.28</v>
+        <v>3332.47</v>
       </c>
     </row>
     <row r="662">
@@ -40829,7 +40829,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>16006.71</v>
+        <v>16482.48</v>
       </c>
     </row>
     <row r="663">
@@ -40890,7 +40890,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>3111.01</v>
+        <v>3203.48</v>
       </c>
     </row>
     <row r="664">
@@ -40951,7 +40951,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>9302.459999999999</v>
+        <v>9578.959999999999</v>
       </c>
     </row>
     <row r="665">
@@ -41012,7 +41012,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>11391.33</v>
+        <v>11729.91</v>
       </c>
     </row>
     <row r="666">
@@ -41073,7 +41073,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>995.3</v>
+        <v>1024.88</v>
       </c>
     </row>
     <row r="667">
@@ -41134,7 +41134,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>1046.21</v>
+        <v>1077.31</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38491,7 +38491,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38857,7 +38857,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -39711,7 +39711,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -40504,7 +40504,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40870,7 +40870,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -41053,7 +41053,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2026.xlsx
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ADM. FINANCIERO DEL SISTEMA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE AYSEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FRE</t>
+          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FREI MONTALVA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE DEPARTAMENTO COMUNAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION VI REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>ADM. FINANCIERO DEL SISTEMA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE DEPARTAMENTO COMUNAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Centro de Sangre y Tejidos de Concepcion</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17014,12 +17014,12 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA PESCA ARTESANAL Y A</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Rompehielos AGB 46 Almirante Viel</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DIRECCION DE RECUPERACION DE UNIDADES DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Departamento de Salud Parral</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Instituto Nacional de Neurocirugía</t>
+          <t>Instituto de Neurocirugía</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO SALUD MUNICIPALIDAD DE QUILLON</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21101,7 +21101,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO SALUD MUNICIPALIDAD DE QUILLON</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21955,7 +21955,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -24090,7 +24090,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>INGESCOM LTDA.</t>
+          <t>Ingescom ltda.</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
@@ -24212,7 +24212,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Tribunal de Juicio Oral en lo Penal de Copiapo</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -26286,7 +26286,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE VALPARAISO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27262,7 +27262,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -27445,7 +27445,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -27567,7 +27567,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27923,7 +27923,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -27994,7 +27994,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -28970,7 +28970,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -29641,7 +29641,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -29702,7 +29702,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -30007,7 +30007,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -30129,7 +30129,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Rosendo - Salud</t>
+          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -30434,7 +30434,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA METROPOLITANA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -30861,7 +30861,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -32020,7 +32020,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -32081,7 +32081,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -32142,7 +32142,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -32386,7 +32386,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32935,7 +32935,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -33057,7 +33057,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33179,7 +33179,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -33240,7 +33240,7 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -33484,7 +33484,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CET Calama</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -33911,7 +33911,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universidad de Chile </t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -33972,7 +33972,7 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -34155,7 +34155,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -34277,7 +34277,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -34338,7 +34338,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -34948,7 +34948,7 @@
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Esta</t>
+          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -35009,7 +35009,7 @@
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -35497,7 +35497,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -35680,7 +35680,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -36961,7 +36961,7 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -37144,12 +37144,12 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37571,7 +37571,7 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -37693,7 +37693,7 @@
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -38059,7 +38059,7 @@
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>DEPTO HABITABILIDAD COMANDANCIA EN JEFE DE 1 Z. N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -38120,7 +38120,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>ESCUELA DE GRUMETES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -38303,7 +38303,7 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -38364,7 +38364,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -38547,7 +38547,7 @@
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>JUZGADO DE GARANTIA DE COPIAPO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -38974,7 +38974,7 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -39096,7 +39096,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -39279,7 +39279,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -39950,7 +39950,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -40072,7 +40072,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Esta</t>
+          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -40194,7 +40194,7 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -40565,7 +40565,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40621,7 +40621,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CASTRO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -40743,7 +40743,7 @@
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1590,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1716,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1842,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1907,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1972,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2037,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2102,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2167,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2232,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2297,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2427,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2492,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2618,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2683,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2748,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2813,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2878,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2943,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3008,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3138,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3203,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3455,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3581,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3646,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3711,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3776,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3902,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4089,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4154,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4219,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4345,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4410,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4475,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4601,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4666,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4792,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4857,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5044,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5109,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5174,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5239,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5365,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5613,11 @@
           <t>77.911.731-6</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5678,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5804,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5930,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5995,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6060,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6125,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6190,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6499,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6564,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6629,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6694,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6759,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6824,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6889,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7015,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7080,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7145,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7210,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7275,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7401,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7466,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7592,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7657,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7722,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7787,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8039,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8104,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8230,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8295,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8360,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8425,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8490,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8555,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8620,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8685,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8750,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8815,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8880,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8945,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9071,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9136,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9201,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9266,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9331,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9396,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9461,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9526,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9591,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9656,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9721,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9786,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9851,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9916,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9981,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10107,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10172,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10237,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10302,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10367,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10493,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10558,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10623,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10688,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10753,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10818,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10944,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11009,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11074,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11139,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11265,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11330,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11395,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11460,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11525,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11590,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11655,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11720,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11846,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11911,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11976,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12041,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12106,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12171,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12236,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12301,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12366,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12431,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12496,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12561,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12626,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12691,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12756,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12821,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12951,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13138,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13203,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13268,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13455,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13520,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13585,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13650,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13715,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13780,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13845,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13971,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14097,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14162,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14227,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14536,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14601,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14666,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14731,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14796,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14861,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14926,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14991,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15056,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15121,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15186,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15251,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15316,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15381,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15507,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15572,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15637,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15702,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15767,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15893,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15958,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16084,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16149,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16214,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16279,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16344,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16409,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16474,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16539,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16604,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16669,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16734,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16799,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16864,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16990,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17055,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17120,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17185,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17250,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17376,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17441,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17506,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17571,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17636,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17701,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17766,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17831,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17896,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17961,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18026,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18091,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18156,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18221,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18286,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18351,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18416,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18725,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18790,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18855,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18920,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18985,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19050,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19115,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19180,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19306,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19371,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19436,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19562,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19627,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19692,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19757,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19822,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19887,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20017,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20082,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20147,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20212,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20277,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20464,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20594,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20659,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20724,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20789,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20976,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21041,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21106,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21171,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21236,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21301,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21366,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21431,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21557,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21683,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21748,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21813,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21878,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21943,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22138,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22203,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22451,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22516,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22642,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22707,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22772,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22837,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22902,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22967,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23032,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23097,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23162,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23227,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23292,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23357,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23422,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23487,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23552,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23617,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23682,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23747,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23812,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23938,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +24003,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24194,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24259,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24324,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24450,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24515,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24645,11 @@
           <t>77.979.117-3</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24832,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24897,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +25023,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25088,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25153,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25218,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25405,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25592,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25657,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25722,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25787,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25917,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25982,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +26047,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26112,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26177,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26242,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26429,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26494,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26559,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26624,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26811,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26876,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26941,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +27006,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27071,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27197,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27262,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27327,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27392,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27457,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27522,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27587,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27652,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27717,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27782,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27847,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27912,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27977,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +28042,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28107,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28172,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28237,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28363,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28428,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28493,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28558,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28623,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28688,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28818,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28883,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +29009,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29200,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29265,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29330,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29395,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29525,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29590,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29720,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29785,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29911,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29976,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +30041,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +30106,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30171,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30297,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30362,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30427,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30492,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30557,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30622,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30687,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30752,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30878,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30943,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +31008,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +31073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31138,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31203,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +31329,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31394,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31459,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31585,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31711,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31776,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31963,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +32028,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +32093,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32158,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32223,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32288,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32353,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32418,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32483,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32548,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32613,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +32678,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32743,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32869,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32934,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32999,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +33064,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +33129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +33194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33259,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33324,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33389,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33454,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33519,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33584,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33649,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +33714,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33779,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33844,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33909,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33974,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +34039,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +34104,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34169,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34234,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +34299,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34425,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34490,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34555,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34620,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34685,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +34750,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +34815,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34941,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +35006,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +35071,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +35197,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +35262,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35327,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +35392,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35457,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35522,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +35709,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35835,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35900,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35965,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +36030,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +36095,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +36160,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +36225,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34478,7 +36290,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +36355,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +36420,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +36485,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36611,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +36676,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36741,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34966,7 +36806,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35027,7 +36871,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36936,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +37062,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +37127,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +37253,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +37318,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +37383,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +37448,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +37513,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37578,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35759,7 +37643,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +37708,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37773,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35942,7 +37838,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36003,7 +37903,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37968,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +38094,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +38159,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +38224,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +38289,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +38354,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +38419,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +38484,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +38549,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +38614,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38679,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +38805,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38870,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38935,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37040,7 +39000,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +39065,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +39191,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +39256,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37406,7 +39382,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +39447,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +39512,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +39577,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39642,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +39707,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +39772,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37833,7 +39837,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39902,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38016,7 +40028,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +40154,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38199,7 +40219,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38260,7 +40284,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +40349,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38443,7 +40475,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38504,7 +40540,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38565,7 +40605,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38626,7 +40670,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38687,7 +40735,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38748,7 +40800,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38809,7 +40865,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38931,7 +40991,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39053,7 +41117,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39114,7 +41182,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39175,7 +41247,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39236,7 +41312,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39297,7 +41377,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39358,7 +41442,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39419,7 +41507,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39541,7 +41633,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +41698,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +41763,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +41828,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39846,7 +41954,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39907,7 +42019,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39968,7 +42084,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40029,7 +42149,11 @@
           <t>78.069.505-6</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +42214,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40151,7 +42279,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40212,7 +42344,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40273,7 +42409,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40334,7 +42474,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40395,7 +42539,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40456,7 +42604,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +42669,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40578,7 +42734,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40639,7 +42799,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40700,7 +42864,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40761,7 +42929,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40822,7 +42994,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40883,7 +43059,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40944,7 +43124,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41005,7 +43189,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41066,7 +43254,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41127,7 +43319,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2026.xlsx
@@ -15028,7 +15028,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -24487,7 +24487,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -30659,7 +30659,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
